--- a/astro-site/public/dl/kit-tareas-pasteleria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/05-tareas-semanales-mensuales.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Limpieza Semanal" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mantenimiento Mensual" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Inventario" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Limpieza Semanal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mantenimiento Mensual" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Limpieza Semanal'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mantenimiento Mensual'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Inventario'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,6 +96,12 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -131,7 +141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -153,63 +163,113 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="31">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -571,13 +631,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B8"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -585,6 +646,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -620,8 +682,24 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -630,18 +708,18 @@
   <sheetPr>
     <tabColor rgb="00E91E63"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -658,10 +736,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -701,18 +780,16 @@
           <t xml:space="preserve">  Obrador / Zona de Producción</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="28" t="n"/>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="28" t="n"/>
+      <c r="G5" s="29" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="30" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -738,10 +815,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="30" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -767,10 +842,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="30" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -796,10 +869,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="30" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -825,10 +896,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="30" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -854,10 +923,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="30" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -883,10 +950,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="30" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -912,10 +977,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="30" t="n">
+        <v>8</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -940,24 +1003,23 @@
       <c r="F13" s="14" t="n"/>
       <c r="G13" s="15" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cámaras y Almacén</t>
         </is>
       </c>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="B15" s="28" t="n"/>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="29" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="30" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -983,10 +1045,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="30" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1012,10 +1072,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="30" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1041,10 +1099,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="30" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1070,10 +1126,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="30" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1099,10 +1153,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="30" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1127,24 +1179,23 @@
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="15" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  Vitrinas y Despacho</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
-      <c r="G23" s="19" t="n"/>
+      <c r="B23" s="28" t="n"/>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="28" t="n"/>
+      <c r="E23" s="28" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="29" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="30" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1170,10 +1221,8 @@
       <c r="G24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="30" t="n">
+        <v>16</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1199,10 +1248,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="30" t="n">
+        <v>17</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -1228,10 +1275,8 @@
       <c r="G26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="30" t="n">
+        <v>18</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -1256,6 +1301,8 @@
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="15" t="n"/>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
         <is>
@@ -1264,7 +1311,7 @@
       </c>
       <c r="D30" s="21">
         <f>COUNTIF(F5:F28,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
@@ -1275,6 +1322,7 @@
         <v>18</v>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="21" t="inlineStr">
         <is>
@@ -1282,13 +1330,17 @@
         </is>
       </c>
       <c r="B32" s="15" t="n"/>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="29" t="n"/>
       <c r="E32" s="21" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F32" s="15" t="n"/>
-    </row>
+      <c r="G32" s="29" t="n"/>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="23" t="inlineStr">
         <is>
@@ -1308,11 +1360,20 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20 F21 F24 F25 F26 F27" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20 F21 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1321,18 +1382,18 @@
   <sheetPr>
     <tabColor rgb="00FF9800"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1349,10 +1410,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1392,18 +1454,16 @@
           <t xml:space="preserve">  Hornos</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="25" t="n"/>
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="28" t="n"/>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="28" t="n"/>
+      <c r="G5" s="29" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="30" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1429,10 +1489,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="30" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1458,10 +1516,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="30" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1487,10 +1543,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="30" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1515,24 +1569,23 @@
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="15" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Equipos de Frío</t>
         </is>
       </c>
-      <c r="B11" s="25" t="n"/>
-      <c r="C11" s="25" t="n"/>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="25" t="n"/>
-      <c r="G11" s="25" t="n"/>
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="29" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="30" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -1558,10 +1611,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="30" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1587,10 +1638,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="30" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1616,10 +1665,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="30" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1644,24 +1691,23 @@
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="15" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Otros Equipos</t>
         </is>
       </c>
-      <c r="B17" s="25" t="n"/>
-      <c r="C17" s="25" t="n"/>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="n"/>
-      <c r="G17" s="25" t="n"/>
+      <c r="B17" s="28" t="n"/>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="29" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="30" t="n">
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1687,10 +1733,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="30" t="n">
+        <v>10</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1716,10 +1760,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="30" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1745,10 +1787,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="30" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1774,10 +1814,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="30" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1802,6 +1840,8 @@
       <c r="F22" s="14" t="n"/>
       <c r="G22" s="15" t="n"/>
     </row>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="21" t="inlineStr">
         <is>
@@ -1810,7 +1850,7 @@
       </c>
       <c r="D25" s="21">
         <f>COUNTIF(F5:F23,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E25" s="22" t="inlineStr">
         <is>
@@ -1821,6 +1861,7 @@
         <v>13</v>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="21" t="inlineStr">
         <is>
@@ -1828,13 +1869,17 @@
         </is>
       </c>
       <c r="B27" s="15" t="n"/>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="29" t="n"/>
       <c r="E27" s="21" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F27" s="15" t="n"/>
-    </row>
+      <c r="G27" s="29" t="n"/>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
         <is>
@@ -1845,8 +1890,8 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="F27:G27"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A25:C25"/>
@@ -1854,11 +1899,20 @@
     <mergeCell ref="A11:G11"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F22" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1867,18 +1921,18 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1895,10 +1949,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1938,18 +1993,16 @@
           <t xml:space="preserve">  Ingredientes Principales</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="28" t="n"/>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="28" t="n"/>
+      <c r="G5" s="29" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="30" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1975,10 +2028,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="30" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -2004,10 +2055,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="30" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -2033,10 +2082,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="30" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -2062,10 +2109,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="30" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -2091,10 +2136,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="30" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -2120,10 +2163,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="30" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -2148,24 +2189,23 @@
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="15" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Ingredientes Secundarios y Decoración</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="29" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="30" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -2191,10 +2231,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="30" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2220,10 +2258,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="30" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2249,10 +2285,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="30" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -2278,10 +2312,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="30" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -2307,10 +2339,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="30" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -2335,6 +2365,8 @@
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="15" t="n"/>
     </row>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
         <is>
@@ -2343,7 +2375,7 @@
       </c>
       <c r="D23" s="21">
         <f>COUNTIF(F5:F21,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
@@ -2354,6 +2386,7 @@
         <v>13</v>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="21" t="inlineStr">
         <is>
@@ -2361,13 +2394,17 @@
         </is>
       </c>
       <c r="B25" s="15" t="n"/>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="29" t="n"/>
       <c r="E25" s="21" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F25" s="15" t="n"/>
-    </row>
+      <c r="G25" s="29" t="n"/>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
         <is>
@@ -2386,10 +2423,19 @@
     <mergeCell ref="B25:D25"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-pasteleria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/05-tareas-semanales-mensuales.xlsx
@@ -269,6 +269,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -686,14 +696,15 @@
     <row r="10">
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -710,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -765,7 +776,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1301,48 +1312,84 @@
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="15" t="n"/>
     </row>
-    <row r="28"/>
-    <row r="29"/>
+    <row r="28">
+      <c r="A28" s="30" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="15" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="15" t="n"/>
+    </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="30" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="15" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="30" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="15" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D30" s="21">
-        <f>COUNTIF(F5:F28,"✓")</f>
+      <c r="D33" s="21">
+        <f>COUNTIF(F5:F31,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F30" s="21" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="F33" s="21">
+        <f>COUNTIF(B5:B31,"?*")</f>
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="28" t="n"/>
-      <c r="D32" s="29" t="n"/>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="28" t="n"/>
+      <c r="D35" s="29" t="n"/>
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="29" t="n"/>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="29" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -1350,18 +1397,23 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A33:C33"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G31">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20 F21 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20 F21 F24 F25 F26 F27 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1384,7 +1436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1439,7 +1491,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1616,7 +1668,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Verificar temperaturas reales vs. display (sonda independiente)</t>
+          <t>Verificar temperaturas reales vs. display (sonda independiente) → 13 Registro de Temperaturas</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
@@ -1840,48 +1892,84 @@
       <c r="F22" s="14" t="n"/>
       <c r="G22" s="15" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24"/>
+    <row r="23">
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="26" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="15" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="15" t="n"/>
+    </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="15" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="15" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D25" s="21">
-        <f>COUNTIF(F5:F23,"✓")</f>
+      <c r="D28" s="21">
+        <f>COUNTIF(F5:F26,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F25" s="21" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="F28" s="21">
+        <f>COUNTIF(B5:B26,"?*")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="28" t="n"/>
-      <c r="D27" s="29" t="n"/>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="29" t="n"/>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="29" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -1889,18 +1977,23 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G26">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1923,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1978,7 +2071,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2365,48 +2458,84 @@
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="15" t="n"/>
     </row>
-    <row r="21"/>
-    <row r="22"/>
+    <row r="21">
+      <c r="A21" s="30" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="15" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="15" t="n"/>
+    </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="15" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="15" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D23" s="21">
-        <f>COUNTIF(F5:F21,"✓")</f>
+      <c r="D26" s="21">
+        <f>COUNTIF(F5:F24,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F23" s="21" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="F26" s="21">
+        <f>COUNTIF(B5:B24,"?*")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="28" t="n"/>
-      <c r="D25" s="29" t="n"/>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="29" t="n"/>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="29" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -2414,17 +2543,22 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F28:G28"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B28:D28"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G24">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
